--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -135,6 +135,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -675,12 +684,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>최근 갱신</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 Windows에서만 재검증. 앞으로 Windows 작업 중 macOS 전용 로직은 건드리지 않는 방향.</t>
+          <t>2026-07-03 Windows: 로그인 후 위젯 실행 전에 Tauri 저장 프로젝트룸과 서버 위젯 컨텍스트를 복구하도록 보강. CSV는 추적 제외 정책 유지.</t>
         </is>
       </c>
     </row>
@@ -781,7 +790,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="10" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -831,7 +840,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -881,32 +890,32 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>65</v>
+      <c r="D4" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지는 바 복원 항목 시드(#162)</t>
+          <t>bar+todo 표시, 나머지 바 복원 항목 시드, 실행 전 Tauri 저장 프로젝트룸/서버 위젯 컨텍스트 복구</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 Windows 실사용 확인</t>
+          <t>실제 OAuth 후 Windows GUI 왕복과 깜빡임 재발 확인</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원</t>
+          <t>로그인 후 bar/todo 표시, 각 위젯 복원, 초기 roomId 유지</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>#162</t>
+          <t>src/lib/tauri/authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>창 다중 오픈/깜빡임 재발 확인</t>
+          <t>macOS 전용 로직 수정 없이 공통 프론트 런처만 보강</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -931,7 +940,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -981,7 +990,7 @@
           <t>꽤 됨</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="11" t="n">
         <v>80</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1031,7 +1040,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="10" t="n">
         <v>70</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1081,7 +1090,7 @@
           <t>부분</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1131,7 +1140,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1181,7 +1190,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1231,7 +1240,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1281,7 +1290,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1331,7 +1340,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1381,7 +1390,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1431,7 +1440,7 @@
           <t>문제</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="12" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1481,7 +1490,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="12" t="n">
         <v>40</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1531,7 +1540,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="10" t="n">
         <v>70</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1581,7 +1590,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1631,7 +1640,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="12" t="n">
         <v>55</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1681,7 +1690,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="12" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1731,7 +1740,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1781,7 +1790,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="12" t="n">
         <v>55</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1831,7 +1840,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1982,7 +1991,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="10" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2032,7 +2041,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2082,32 +2091,32 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>65</v>
+      <c r="D4" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지는 바 복원 항목 시드(#162)</t>
+          <t>bar+todo 표시, 나머지 바 복원 항목 시드, 실행 전 Tauri 저장 프로젝트룸/서버 위젯 컨텍스트 복구</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 Windows 실사용 확인</t>
+          <t>실제 OAuth 후 Windows GUI 왕복과 깜빡임 재발 확인</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원</t>
+          <t>로그인 후 bar/todo 표시, 각 위젯 복원, 초기 roomId 유지</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>#162</t>
+          <t>src/lib/tauri/authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>창 다중 오픈/깜빡임 재발 확인</t>
+          <t>macOS 전용 로직 수정 없이 공통 프론트 런처만 보강</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2132,7 +2141,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2182,7 +2191,7 @@
           <t>꽤 됨</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="11" t="n">
         <v>80</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2232,7 +2241,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="10" t="n">
         <v>70</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2282,7 +2291,7 @@
           <t>부분</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2332,7 +2341,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2382,7 +2391,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2432,7 +2441,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2482,7 +2491,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="11" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: 로그인 후 위젯 실행 전에 Tauri 저장 프로젝트룸과 서버 위젯 컨텍스트를 복구하도록 보강. CSV는 추적 제외 정책 유지.</t>
+          <t>2026-07-03 Windows: activity consent resend fixed; real-backend smoke now covers /api/activity/current-app and /api/activity/today. macOS-specific logic untouched.</t>
         </is>
       </c>
     </row>
@@ -1087,35 +1087,35 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>승인 이벤트를 /api/local-file-events/sync로 전송</t>
+          <t>Approved local file events include localEventId and real-backend smoke verifies CREATED/DELETED -&gt; SYNCED.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>localEventId 매칭 PR #158 머지와 실백엔드 왕복</t>
+          <t>GUI watch/outbox long-run QA and SQLite state inspection still remain.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>sync 후 올바른 이벤트가 SYNCED/FAILED</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync with created/deleted events.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>#158</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>현재 체크아웃에는 #158 미포함</t>
+          <t>CSV remains untracked; xlsx is the tracked checklist artifact.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1137,35 +1137,35 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground window/process 감지, 동의 기반 30초 자동 캡처</t>
+          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>실사용 dwell time 검증</t>
+          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>앱 전환 시 appName/windowTitle 기록, /api/activity/today 반영</t>
+          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>activity.rs, activity-client.ts</t>
+          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows 전용 로직 유지</t>
+          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2288,35 +2288,35 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>승인 이벤트를 /api/local-file-events/sync로 전송</t>
+          <t>Approved local file events include localEventId and real-backend smoke verifies CREATED/DELETED -&gt; SYNCED.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>localEventId 매칭 PR #158 머지와 실백엔드 왕복</t>
+          <t>GUI watch/outbox long-run QA and SQLite state inspection still remain.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>sync 후 올바른 이벤트가 SYNCED/FAILED</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync with created/deleted events.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>#158</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>현재 체크아웃에는 #158 미포함</t>
+          <t>CSV remains untracked; xlsx is the tracked checklist artifact.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2338,35 +2338,35 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground window/process 감지, 동의 기반 30초 자동 캡처</t>
+          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>실사용 dwell time 검증</t>
+          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>앱 전환 시 appName/windowTitle 기록, /api/activity/today 반영</t>
+          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>activity.rs, activity-client.ts</t>
+          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows 전용 로직 유지</t>
+          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>로컬 파일/활동/SQLite 실백엔드 왕복</t>
+          <t>Local file/activity/SQLite real-backend and GUI QA follow-up</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SQLite 상태와 서버 응답 일치</t>
+          <t>API smoke passes; GUI SQLite/watch/runtime evidence captured separately</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>실백엔드 + Docker 환경</t>
+          <t>npm.cmd run dev:widget:backend + Tauri GUI QA</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>#158 병합 여부 확인</t>
+          <t>Do not modify macOS-specific logic</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3689,6 +3689,28 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Real backend API smoke</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>widget, chat, local-file sync, activity, summaries pass against Docker/backend</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: activity consent resend fixed; real-backend smoke now covers /api/activity/current-app and /api/activity/today. macOS-specific logic untouched.</t>
+          <t>2026-07-03 Windows: widget launch failure path no longer starts background sync or marks surfaces launched; activity/local-file backend smoke retained. macOS-specific logic untouched.</t>
         </is>
       </c>
     </row>
@@ -887,35 +887,35 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지 바 복원 항목 시드, 실행 전 Tauri 저장 프로젝트룸/서버 위젯 컨텍스트 복구</t>
+          <t>Login starts app + widget surfaces, restores server/Tauri room context, and does not mark launch complete when all widget opens fail.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>실제 OAuth 후 Windows GUI 왕복과 깜빡임 재발 확인</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close QA and flicker regression check remain.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원, 초기 roomId 유지</t>
+          <t>typecheck, tauri-boundaries, and real-backend smoke; GUI evidence still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>src/lib/tauri/authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
+          <t>#164, authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS 전용 로직 수정 없이 공통 프론트 런처만 보강</t>
+          <t>macOS-specific launcher/window logic untouched; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지 바 복원 항목 시드, 실행 전 Tauri 저장 프로젝트룸/서버 위젯 컨텍스트 복구</t>
+          <t>Login starts app + widget surfaces, restores server/Tauri room context, and does not mark launch complete when all widget opens fail.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>실제 OAuth 후 Windows GUI 왕복과 깜빡임 재발 확인</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close QA and flicker regression check remain.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원, 초기 roomId 유지</t>
+          <t>typecheck, tauri-boundaries, and real-backend smoke; GUI evidence still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>src/lib/tauri/authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
+          <t>#164, authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS 전용 로직 수정 없이 공통 프론트 런처만 보강</t>
+          <t>macOS-specific launcher/window logic untouched; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3711,6 +3711,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Widget launch failure retry</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Code path + typecheck + tauri-boundaries</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>All-open failure leaves launched flag false and avoids starting background runtimes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget launch failure path no longer starts background sync or marks surfaces launched; activity/local-file backend smoke retained. macOS-specific logic untouched.</t>
+          <t>2026-07-03 Windows: desktop widget real-data path now reads backend widget summary first and uses Tauri cache only as fallback for tasks, schedules, timer, unread count, and agent summary. CSV remains untracked.</t>
         </is>
       </c>
     </row>
@@ -1187,35 +1187,35 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>로컬 상세 이벤트, rollup, 서버 usage summary 동기화</t>
+          <t>Widget summary type matches backend extended fields; desktop widget reads server summary first, then falls back to Tauri summary cache for tasks, schedules, timer, unread count, and agent summary.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>실서버 settings 매칭 실패 케이스 QA</t>
+          <t>GUI evidence for stale-cache/server-down visual behavior still remains.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>위젯 조작 후 rollup sync</t>
+          <t>typecheck, product-rules, tauri-boundaries, and real-backend smoke verify server summary/settings contract.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>widget_usage.rs</t>
+          <t>#164, desktop-widget/page.tsx, types/api/widget.ts, widgetDisplayApi.ts</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>장시간 동기화 확인</t>
+          <t>Avoid preview/mock fallback in Tauri real data path; macOS-specific logic untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2388,35 +2388,35 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>로컬 상세 이벤트, rollup, 서버 usage summary 동기화</t>
+          <t>Widget summary type matches backend extended fields; desktop widget reads server summary first, then falls back to Tauri summary cache for tasks, schedules, timer, unread count, and agent summary.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>실서버 settings 매칭 실패 케이스 QA</t>
+          <t>GUI evidence for stale-cache/server-down visual behavior still remains.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>위젯 조작 후 rollup sync</t>
+          <t>typecheck, product-rules, tauri-boundaries, and real-backend smoke verify server summary/settings contract.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>widget_usage.rs</t>
+          <t>#164, desktop-widget/page.tsx, types/api/widget.ts, widgetDisplayApi.ts</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>장시간 동기화 확인</t>
+          <t>Avoid preview/mock fallback in Tauri real data path; macOS-specific logic untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3733,6 +3733,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Desktop widget summary fallback</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Backend summary extended fields are typed and can populate widget display fallback/cache</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: desktop widget real-data path now reads backend widget summary first and uses Tauri cache only as fallback for tasks, schedules, timer, unread count, and agent summary. CSV remains untracked.</t>
+          <t>2026-07-03 Windows: widget usage rollup sync now marks failed/mismatched server sends in SQLite for retry while keeping raw events local; server-first widget display fallback retained. CSV remains untracked.</t>
         </is>
       </c>
     </row>
@@ -1191,31 +1191,31 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget summary type matches backend extended fields; desktop widget reads server summary first, then falls back to Tauri summary cache for tasks, schedules, timer, unread count, and agent summary.</t>
+          <t>Widget display uses server-first summary fallback; widget usage rollups now mark failed/mismatched server sync attempts in SQLite for retry without losing raw local events.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>GUI evidence for stale-cache/server-down visual behavior still remains.</t>
+          <t>Long-running GUI usage sync QA still remains.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>typecheck, product-rules, tauri-boundaries, and real-backend smoke verify server summary/settings contract.</t>
+          <t>cargo test --lib covers widget usage failed retry state; typecheck/product-rules/tauri-boundaries pass.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, desktop-widget/page.tsx, types/api/widget.ts, widgetDisplayApi.ts</t>
+          <t>#164, widget_usage.rs, widget-local-client.ts, commands.ts</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Avoid preview/mock fallback in Tauri real data path; macOS-specific logic untouched.</t>
+          <t>Detailed widget usage events remain local; only rollups are server synced. macOS-specific logic untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2392,31 +2392,31 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget summary type matches backend extended fields; desktop widget reads server summary first, then falls back to Tauri summary cache for tasks, schedules, timer, unread count, and agent summary.</t>
+          <t>Widget display uses server-first summary fallback; widget usage rollups now mark failed/mismatched server sync attempts in SQLite for retry without losing raw local events.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>GUI evidence for stale-cache/server-down visual behavior still remains.</t>
+          <t>Long-running GUI usage sync QA still remains.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>typecheck, product-rules, tauri-boundaries, and real-backend smoke verify server summary/settings contract.</t>
+          <t>cargo test --lib covers widget usage failed retry state; typecheck/product-rules/tauri-boundaries pass.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, desktop-widget/page.tsx, types/api/widget.ts, widgetDisplayApi.ts</t>
+          <t>#164, widget_usage.rs, widget-local-client.ts, commands.ts</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Avoid preview/mock fallback in Tauri real data path; macOS-specific logic untouched.</t>
+          <t>Detailed widget usage events remain local; only rollups are server synced. macOS-specific logic untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3755,6 +3755,28 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Widget usage rollup retry</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cd src-tauri; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Failed or unmatched usage rollups are marked FAILED in SQLite and remain retry candidates</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +83,21 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -110,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +159,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -689,7 +713,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget usage rollup sync now marks failed/mismatched server sends in SQLite for retry while keeping raw events local; server-first widget display fallback retained. CSV remains untracked.</t>
+          <t>2026-07-03 Windows: latest develop rebased; widget window open now waits for real Tauri window creation, existing widgets reapply preferred-monitor positions, close-all and room context persist immediately. macOS-specific logic untouched; Mac widget fix remains Mac team owned.</t>
         </is>
       </c>
     </row>
@@ -790,7 +814,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -840,7 +864,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="13" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -890,22 +914,22 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>72</v>
+      <c r="D4" s="13" t="n">
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login starts app + widget surfaces, restores server/Tauri room context, and does not mark launch complete when all widget opens fail.</t>
+          <t>Login opens bar + primary widget after auth; widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Real OAuth Windows GUI relaunch/minimize/close QA and flicker regression check remain.</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close/flicker regression QA remains.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>typecheck, tauri-boundaries, and real-backend smoke; GUI evidence still required.</t>
+          <t>cargo fmt/check/tests plus PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -937,35 +961,35 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>열기/닫기/최소화/복원/항상 위/고스트/위치 저장</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>투명창, 무테두리, 그림자 GUI QA</t>
+          <t>Transparent frameless shadow and no-scrollbar GUI capture QA.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>창 테두리 없음, 스크롤바 없음, 드래그 가능</t>
+          <t>cargo test --lib; actual Windows Tauri screen capture must show no border/scrollbar/titlebar flicker.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>src-tauri/src/lib.rs, desktop-widget</t>
+          <t>#164, src-tauri/src/lib.rs, desktop-widget</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView shadow/transparent 확인</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS-specific cfg untouched.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -990,7 +1014,7 @@
           <t>꽤 됨</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="14" t="n">
         <v>80</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1040,7 +1064,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1090,7 +1114,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1190,7 +1214,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="14" t="n">
         <v>82</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1290,7 +1314,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="13" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1340,7 +1364,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1440,7 +1464,7 @@
           <t>문제</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1490,7 +1514,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="15" t="n">
         <v>40</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1540,7 +1564,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1640,7 +1664,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="10" t="n">
         <v>55</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1690,7 +1714,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="10" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1790,7 +1814,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="10" t="n">
         <v>55</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1991,7 +2015,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2041,7 +2065,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="13" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2091,22 +2115,22 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>72</v>
+      <c r="D4" s="13" t="n">
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login starts app + widget surfaces, restores server/Tauri room context, and does not mark launch complete when all widget opens fail.</t>
+          <t>Login opens bar + primary widget after auth; widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Real OAuth Windows GUI relaunch/minimize/close QA and flicker regression check remain.</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close/flicker regression QA remains.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>typecheck, tauri-boundaries, and real-backend smoke; GUI evidence still required.</t>
+          <t>cargo fmt/check/tests plus PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2138,35 +2162,35 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>열기/닫기/최소화/복원/항상 위/고스트/위치 저장</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>투명창, 무테두리, 그림자 GUI QA</t>
+          <t>Transparent frameless shadow and no-scrollbar GUI capture QA.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>창 테두리 없음, 스크롤바 없음, 드래그 가능</t>
+          <t>cargo test --lib; actual Windows Tauri screen capture must show no border/scrollbar/titlebar flicker.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>src-tauri/src/lib.rs, desktop-widget</t>
+          <t>#164, src-tauri/src/lib.rs, desktop-widget</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView shadow/transparent 확인</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS-specific cfg untouched.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2191,7 +2215,7 @@
           <t>꽤 됨</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="14" t="n">
         <v>80</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2241,7 +2265,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2291,7 +2315,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="13" t="n">
         <v>70</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2391,7 +2415,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="14" t="n">
         <v>82</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2491,7 +2515,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="13" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3210,7 +3234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3442,6 +3466,38 @@
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Do not modify macOS-specific logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Windows widget window runtime stabilization GUI QA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>No delayed wave/flicker after login; preferred monitor move reapplies to visible widgets; close-all leaves no widget windows.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>npm.cmd run tauri:dev:backend + Windows screen capture; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Do not touch macOS-specific widget/app logic.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3777,6 +3833,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Widget window runtime stabilization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cd src-tauri; cargo test --lib; then Windows Tauri GUI smoke</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>open_widget_window waits for real window creation; existing widgets move with preferred monitor; room context/close-all persist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: latest develop rebased; widget window open now waits for real Tauri window creation, existing widgets reapply preferred-monitor positions, close-all and room context persist immediately. macOS-specific logic untouched; Mac widget fix remains Mac team owned.</t>
+          <t>2026-07-03 Windows: latest backend/frontend develop verified; real-backend widget smoke passed. Windows/non-mac widget open now waits for real Tauri window creation, existing visible widgets reapply preferred-monitor positions, close-all and room context persist immediately. macOS keeps the previous async widget build path for Mac-team work.</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login opens bar + primary widget after auth; widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>cargo fmt/check/tests plus PR CI; GUI capture still required.</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS-specific launcher/window logic untouched; Mac team owns Mac widget fix.</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Open/close/minimize/restore/topmost/ghost/position store; existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; Windows/non-mac existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView transparent/shadow QA still required; macOS-specific cfg untouched.</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS async build path preserved.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login opens bar + primary widget after auth; widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>cargo fmt/check/tests plus PR CI; GUI capture still required.</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS-specific launcher/window logic untouched; Mac team owns Mac widget fix.</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Open/close/minimize/restore/topmost/ghost/position store; existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; Windows/non-mac existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView transparent/shadow QA still required; macOS-specific cfg untouched.</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS async build path preserved.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cd src-tauri; cargo test --lib; then Windows Tauri GUI smoke</t>
+          <t>cd src-tauri; cargo test --lib; npm.cmd run dev:widget:backend; then Windows Tauri GUI smoke</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>open_widget_window waits for real window creation; existing widgets move with preferred monitor; room context/close-all persist.</t>
+          <t>Windows/non-mac open_widget_window waits for real window creation; existing widgets move with preferred monitor; room context/close-all persist; macOS async build path preserved.</t>
         </is>
       </c>
     </row>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: latest backend/frontend develop verified; real-backend widget smoke passed. Windows/non-mac widget open now waits for real Tauri window creation, existing visible widgets reapply preferred-monitor positions, close-all and room context persist immediately. macOS keeps the previous async widget build path for Mac-team work.</t>
+          <t>2026-07-03 Windows: real-backend widget smoke now covers chat plus voice room create/read/mic/leave and optional LiveKit token shape. Widget display voice type accepts backend createdByUserId. macOS widget path remains Mac-team owned.</t>
         </is>
       </c>
     </row>
@@ -1261,35 +1261,35 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>채팅방/메시지 API, 전송, 읽음, 로컬 메시지 캐시, LiveKit 진입 코드</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>실채팅/음성 연결 QA</t>
+          <t>LiveKit in-app audio GUI/mic permission QA and token-backed room join still need live desktop verification.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>메시지 전송/읽음/캐시, 음성방 토큰</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>desktop-widget/page.tsx</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, widgetDisplayApi.ts, desktop-widget/page.tsx</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>마이크 권한 확인</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2462,35 +2462,35 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>채팅방/메시지 API, 전송, 읽음, 로컬 메시지 캐시, LiveKit 진입 코드</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>실채팅/음성 연결 QA</t>
+          <t>LiveKit in-app audio GUI/mic permission QA and token-backed room join still need live desktop verification.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>메시지 전송/읽음/캐시, 음성방 토큰</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>desktop-widget/page.tsx</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, widgetDisplayApi.ts, desktop-widget/page.tsx</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>마이크 권한 확인</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3855,6 +3855,28 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Widget communication voice smoke</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Real backend verifies voice room create/read/mic/leave; token shape is checked when local LiveKit secret allows it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +175,13 @@
     <xf numFmtId="1" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -711,9 +723,9 @@
           <t>최근 갱신</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-03 Windows: real-backend widget smoke now covers chat plus voice room create/read/mic/leave and optional LiveKit token shape. Widget display voice type accepts backend createdByUserId. macOS widget path remains Mac-team owned.</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03 Windows: real-backend smoke now covers chat, voice, local file CREATED/DELETED sync, and /api/local-file-analyses ANALYZE_RESOURCE job creation. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1099,50 +1111,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>로컬 파일 서버 동기화</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>progress</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Approved local file events include localEventId and real-backend smoke verifies CREATED/DELETED -&gt; SYNCED.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>GUI watch/outbox long-run QA and SQLite state inspection still remain.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync with created/deleted events.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>CSV remains untracked; xlsx is the tracked checklist artifact.</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="D8" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Approved local file CREATED/DELETED sync is smoke-tested, and created PERSONAL resource now immediately posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>GUI watch/outbox long-run QA, SQLite row state inspection, and large/permission-denied file cases still remain.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync plus /api/local-file-analyses before delete cleanup.</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts, localFileAnalysisApi.ts</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -1917,6 +1929,16 @@
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
       <formula>60</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2300,50 +2322,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>로컬 파일 서버 동기화</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>progress</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Approved local file events include localEventId and real-backend smoke verifies CREATED/DELETED -&gt; SYNCED.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>GUI watch/outbox long-run QA and SQLite state inspection still remain.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync with created/deleted events.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>CSV remains untracked; xlsx is the tracked checklist artifact.</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="D8" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Approved local file CREATED/DELETED sync is smoke-tested, and created PERSONAL resource now immediately posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>GUI watch/outbox long-run QA, SQLite row state inspection, and large/permission-denied file cases still remain.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync plus /api/local-file-analyses before delete cleanup.</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts, localFileAnalysisApi.ts</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2568,6 +2590,16 @@
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
       <formula>60</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3516,7 +3548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3877,6 +3909,28 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>로컬 파일 분석 서버 왕복</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>/api/local-file-events/sync CREATED returns resourceId, then /api/local-file-analyses returns ANALYZE_RESOURCE job before DELETE cleanup</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke now covers chat, voice, local file CREATED/DELETED sync, and /api/local-file-analyses ANALYZE_RESOURCE job creation. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke now covers chat, voice, local file CREATED/UPDATED/DELETED sync, and /api/local-file-analyses ANALYZE_RESOURCE job creation. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Approved local file CREATED/DELETED sync is smoke-tested, and created PERSONAL resource now immediately posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync plus /api/local-file-analyses before delete cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -1931,6 +1931,16 @@
       <formula>60</formula>
     </cfRule>
     <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="60"/>
@@ -2338,11 +2348,11 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Approved local file CREATED/DELETED sync is smoke-tested, and created PERSONAL resource now immediately posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -2352,7 +2362,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync plus /api/local-file-analyses before delete cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -2592,6 +2602,16 @@
       <formula>60</formula>
     </cfRule>
     <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="60"/>
@@ -3927,7 +3947,7 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>/api/local-file-events/sync CREATED returns resourceId, then /api/local-file-analyses returns ANALYZE_RESOURCE job before DELETE cleanup</t>
+          <t>/api/local-file-events/sync CREATED returns resourceId, UPDATED preserves it, then /api/local-file-analyses returns ANALYZE_RESOURCE job before DELETE cleanup</t>
         </is>
       </c>
     </row>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke now covers chat, voice, local file CREATED/UPDATED/DELETED sync, and /api/local-file-analyses ANALYZE_RESOURCE job creation. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke covers chat, voice, local file CREATED/UPDATED/DELETED sync, /api/local-file-analyses, and activity record/today/delete roundtrip. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1907,6 +1907,56 @@
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Mac 팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>실시간 활동 추적</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>Tauri reads foreground app/window dwell into SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion, and now verifies user delete via DELETE /api/activity/{id}.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Real Windows foreground-app capture GUI evidence, long-running incremental capture, and permission/error UX QA still remain.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks POST /api/activity/current-app, GET /api/activity/today inclusion, DELETE /api/activity/{id}, and /today removal.</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>#164, src/lib/local/activity-client.ts, src-tauri/src/activity.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Windows verification only; macOS activity permission behavior remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
         </is>
       </c>
     </row>
@@ -1951,6 +2001,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D24">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1964,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2576,6 +2638,56 @@
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>실시간 활동 추적</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Tauri reads foreground app/window dwell into SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion, and now verifies user delete via DELETE /api/activity/{id}.</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Real Windows foreground-app capture GUI evidence, long-running incremental capture, and permission/error UX QA still remain.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks POST /api/activity/current-app, GET /api/activity/today inclusion, DELETE /api/activity/{id}, and /today removal.</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>#164, src/lib/local/activity-client.ts, src-tauri/src/activity.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Windows verification only; macOS activity permission behavior remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2612,6 +2724,18 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="60"/>
@@ -3568,7 +3692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3951,6 +4075,28 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>활동 추적 서버 생성/삭제 왕복</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>POST /api/activity/current-app creates a room-scoped record, GET /api/activity/today includes it, DELETE /api/activity/{id} removes it, and /today no longer returns it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke covers chat, voice, local file CREATED/UPDATED/DELETED sync, /api/local-file-analyses, and activity record/today/delete roundtrip. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke covers widget/chat/voice/local file/activity plus privacy consent GET/PATCH for ACTIVITY_CONTEXT and MANAGED_FOLDER. Frontend settings adapter now matches backend consent payload shape. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1955,6 +1955,56 @@
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Full settings GUI toggle QA in real Tauri session remains.</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>#164, settingsApi.ts, settings.ts, settings/page.tsx, privacy-consent-panel.tsx, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2013,6 +2063,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2026,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2750,56 @@
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Full settings GUI toggle QA in real Tauri session remains.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>#164, settingsApi.ts, settings.ts, settings/page.tsx, privacy-consent-panel.tsx, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2746,6 +2858,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D14">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3692,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4097,6 +4221,28 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API contract</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Frontend adapter typechecks; smoke asserts GET /api/me/privacy-consents contains ACTIVITY_CONTEXT and MANAGED_FOLDER, PATCH disables/enables MANAGED_FOLDER, then local file sync proceeds with consent re-enabled</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke covers widget/chat/voice/local file/activity plus privacy consent GET/PATCH for ACTIVITY_CONTEXT and MANAGED_FOLDER. Frontend settings adapter now matches backend consent payload shape. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: activity detection now has Windows-only real foreground capture unit evidence plus backend record/today/delete smoke. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1927,31 +1927,31 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>Tauri reads foreground app/window dwell into SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion, and now verifies user delete via DELETE /api/activity/{id}.</t>
+          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>Real Windows foreground-app capture GUI evidence, long-running incremental capture, and permission/error UX QA still remain.</t>
+          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks POST /api/activity/current-app, GET /api/activity/today inclusion, DELETE /api/activity/{id}, and /today removal.</t>
+          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>#164, src/lib/local/activity-client.ts, src-tauri/src/activity.rs, scripts/dev-widget-real-backend.mjs</t>
+          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>Windows verification only; macOS activity permission behavior remains Mac-team owned.</t>
+          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
@@ -2074,6 +2074,16 @@
         <color rgb="00C6EFCE"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2722,31 +2732,31 @@
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Tauri reads foreground app/window dwell into SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion, and now verifies user delete via DELETE /api/activity/{id}.</t>
+          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Real Windows foreground-app capture GUI evidence, long-running incremental capture, and permission/error UX QA still remain.</t>
+          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks POST /api/activity/current-app, GET /api/activity/today inclusion, DELETE /api/activity/{id}, and /today removal.</t>
+          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>#164, src/lib/local/activity-client.ts, src-tauri/src/activity.rs, scripts/dev-widget-real-backend.mjs</t>
+          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Windows verification only; macOS activity permission behavior remains Mac-team owned.</t>
+          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
@@ -2869,6 +2879,16 @@
         <color rgb="00C6EFCE"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3816,7 +3836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4243,6 +4263,28 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Windows foreground activity capture</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Windows-only test windows_foreground_capture_returns_app_name calls Win32 foreground capture and asserts non-empty app name</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +103,16 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009FD3FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,6 +192,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -723,9 +745,9 @@
           <t>최근 갱신</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03 Windows: activity detection now has Windows-only real foreground capture unit evidence plus backend record/today/delete smoke. macOS app/widget logic remains Mac-team owned and untouched.</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-03 Windows: local folder native watch callback now has direct CREATE/UPDATED/DELETED + FTS add/remove unit evidence; activity/backend smoke evidence remains. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1071,40 +1093,40 @@
           <t>로컬 폴더 트래킹</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>폴더 등록, scan, native watch, FTS 검색, 미리보기, 열기, reindex</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>대용량/삭제/권한/장시간 watch QA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제가 local_file_events에 반영</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>local_files.rs</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Windows notify 경로 확인</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Real Tauri GUI long-run watch QA, large file/permission-denied cases, and SQLite row inspection in an installed app profile.</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_files.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2426,40 +2448,40 @@
           <t>로컬 폴더 트래킹</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>폴더 등록, scan, native watch, FTS 검색, 미리보기, 열기, reindex</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>대용량/삭제/권한/장시간 watch QA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제가 local_file_events에 반영</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>local_files.rs</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Windows notify 경로 확인</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Real Tauri GUI long-run watch QA, large file/permission-denied cases, and SQLite row inspection in an installed app profile.</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_files.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -3978,24 +4000,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>로컬 폴더</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>테스트 폴더 watch</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제 반영</t>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; test folder watch in Tauri GUI</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>CREATED/UPDATED/DELETED events plus FTS add/remove; GUI watch reflects created/modified/deleted files</t>
         </is>
       </c>
     </row>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +113,11 @@
         <fgColor rgb="009FD3FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008FD59D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -140,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,6 +207,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -747,7 +758,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: local folder native watch callback now has direct CREATE/UPDATED/DELETED + FTS add/remove unit evidence; activity/backend smoke evidence remains. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: SQLite integrity check now exposes quick_check, journal mode, page/free counts, DB size, and WAL size in settings; local folder watch and activity/backend smoke evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1043,40 +1054,40 @@
           <t>SQLite</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>꽤 됨</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>bundled rusqlite, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>실앱 장시간 DB 무결성/복구 QA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>quick_check, 백업/복구, 재시작 유지</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>local_db.rs</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>현재 단위테스트 기준만 강함</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>84</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. SQLite integrity IPC now returns quick_check, journal mode, page/free counts, DB size, and WAL size so the settings screen can show concrete local DB diagnostics.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Installed-app long-run DB growth/recovery QA and restore-from-backup relaunch proof remain.</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; full cargo test --lib; settings cache check displays DB/WAL/pages/free details.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/tauri/commands.ts, settings/page.tsx</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Cross-platform SQLite IPC change only; no macOS app/widget window logic touched.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2398,40 +2409,40 @@
           <t>SQLite</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>꽤 됨</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>bundled rusqlite, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>실앱 장시간 DB 무결성/복구 QA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>quick_check, 백업/복구, 재시작 유지</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>local_db.rs</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>현재 단위테스트 기준만 강함</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>84</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. SQLite integrity IPC now returns quick_check, journal mode, page/free counts, DB size, and WAL size so the settings screen can show concrete local DB diagnostics.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Installed-app long-run DB growth/recovery QA and restore-from-backup relaunch proof remain.</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; full cargo test --lib; settings cache check displays DB/WAL/pages/free details.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/tauri/commands.ts, settings/page.tsx</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Cross-platform SQLite IPC change only; no macOS app/widget window logic touched.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -3858,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4307,6 +4318,28 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>SQLite ??</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; settings cache check in Tauri app</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>quick_check ok plus DB/WAL byte sizes, page count, free page count, and journal mode visible from IPC/UI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: SQLite integrity check now exposes quick_check, journal mode, page/free counts, DB size, and WAL size in settings; local folder watch and activity/backend smoke evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: activity auto-capture now performs a best-effort final incremental capture and pending buffer flush when authenticated Tauri surfaces stop; SQLite diagnostics, local folder watch, and backend smoke evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4340,6 +4340,28 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>?? ?? flush</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend; manual Tauri logout/app-close QA</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>On authenticated surface stop, final incremental activity capture and pending buffer sync are attempted before local auto-capture state resets.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: activity auto-capture now performs a best-effort final incremental capture and pending buffer flush when authenticated Tauri surfaces stop; SQLite diagnostics, local folder watch, and backend smoke evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke now covers timer start/heartbeat/pause/resume/stop and verifies dashboard/widget runningTimer reflection; activity flush, SQLite diagnostics, local folder watch evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4362,6 +4362,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>??? ???? ??</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend; cargo test --lib local_db::tests::records_and_recovers_running_timer_state</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Start WORK timer in seeded room, dashboard/widget summary expose runningTimer, heartbeat/pause/resume/stop succeed, local recovery test remains green.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +118,11 @@
         <fgColor rgb="008FD59D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,6 +219,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +769,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke now covers timer start/heartbeat/pause/resume/stop and verifies dashboard/widget runningTimer reflection; activity flush, SQLite diagnostics, local folder watch evidence remain. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke now covers widget item state PATCH with PostgreSQL persistence proof, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, and widget usage retry evidence. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -859,7 +870,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -909,7 +920,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -959,7 +970,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="17" t="n">
         <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1009,7 +1020,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="17" t="n">
         <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1059,7 +1070,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>84</v>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -1109,7 +1120,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="25" t="n">
         <v>74</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -1209,7 +1220,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1260,31 +1271,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; widget usage rollups now mark failed/mismatched server sync attempts in SQLite for retry without losing raw local events.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; real-backend smoke now seeds widget_item_states and verifies PATCH /api/widget/items/{id}/state persists PINNED and CONFIRMED in PostgreSQL.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Long-running GUI usage sync QA still remains.</t>
+          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update the same backend item state without window flicker.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>cargo test --lib covers widget usage failed retry state; typecheck/product-rules/tauri-boundaries pass.</t>
+          <t>npm.cmd run dev:widget:backend verifies item-state PATCH plus DB persistence; cargo test --lib verifies local usage retry behavior.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, widget_usage.rs, widget-local-client.ts, commands.ts</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, desktop-widget, widgetApi.ts, widget_usage.rs</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Detailed widget usage events remain local; only rollups are server synced. macOS-specific logic untouched.</t>
+          <t>Windows/Tauri widget API contract only; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1309,7 +1320,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="17" t="n">
         <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1359,7 +1370,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1409,7 +1420,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="26" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1459,7 +1470,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="26" t="n">
         <v>60</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1509,7 +1520,7 @@
           <t>문제</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="26" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1559,7 +1570,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="26" t="n">
         <v>40</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1609,7 +1620,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1659,7 +1670,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="26" t="n">
         <v>60</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1709,7 +1720,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1759,7 +1770,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1809,7 +1820,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1859,7 +1870,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1909,7 +1920,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2214,7 +2225,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2264,7 +2275,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2314,7 +2325,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="17" t="n">
         <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2364,7 +2375,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="17" t="n">
         <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2414,7 +2425,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>84</v>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -2464,7 +2475,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="25" t="n">
         <v>74</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -2564,7 +2575,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2615,31 +2626,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; widget usage rollups now mark failed/mismatched server sync attempts in SQLite for retry without losing raw local events.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; real-backend smoke now seeds widget_item_states and verifies PATCH /api/widget/items/{id}/state persists PINNED and CONFIRMED in PostgreSQL.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Long-running GUI usage sync QA still remains.</t>
+          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update the same backend item state without window flicker.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>cargo test --lib covers widget usage failed retry state; typecheck/product-rules/tauri-boundaries pass.</t>
+          <t>npm.cmd run dev:widget:backend verifies item-state PATCH plus DB persistence; cargo test --lib verifies local usage retry behavior.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, widget_usage.rs, widget-local-client.ts, commands.ts</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, desktop-widget, widgetApi.ts, widget_usage.rs</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Detailed widget usage events remain local; only rollups are server synced. macOS-specific logic untouched.</t>
+          <t>Windows/Tauri widget API contract only; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2664,7 +2675,7 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="17" t="n">
         <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2714,7 +2725,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3869,7 +3880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4384,6 +4395,28 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state API</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Seeded TODO task item state changes to PINNED then CONFIRMED through /api/widget/items/{id}/state and PostgreSQL confirms persistence.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +225,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke now covers widget item state PATCH with PostgreSQL persistence proof, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, and widget usage retry evidence. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: real-backend smoke covers widget item state, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, and widget usage; widget summary cache is now partitioned by auth subject to avoid stale seed/other-account data. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1070,32 +1073,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>84</v>
+      <c r="D6" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. SQLite integrity IPC now returns quick_check, journal mode, page/free counts, DB size, and WAL size so the settings screen can show concrete local DB diagnostics.</t>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. Widget summary cache is now partitioned by current auth subject so stale seed/other-account widget data is not reused after real login. SQLite integrity IPC returns quick_check, journal mode, page/free counts, DB size, and WAL size.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>Installed-app long-run DB growth/recovery QA and restore-from-backup relaunch proof remain.</t>
+          <t>Installed-app long-run DB growth/recovery QA, restore-from-backup relaunch proof, and real-account cache rollover GUI QA remain.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; full cargo test --lib; settings cache check displays DB/WAL/pages/free details.</t>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; full cargo test --lib; npm.cmd run dev:widget:backend verifies real summary path remains green.</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/local_db.rs, src/lib/tauri/commands.ts, settings/page.tsx</t>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/widget/widget-summary-client.ts, src/lib/tauri/commands.ts</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>Cross-platform SQLite IPC change only; no macOS app/widget window logic touched.</t>
+          <t>Common SQLite/cache contract only; macOS window/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -2425,32 +2428,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>84</v>
+      <c r="D6" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. SQLite integrity IPC now returns quick_check, journal mode, page/free counts, DB size, and WAL size so the settings screen can show concrete local DB diagnostics.</t>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. Widget summary cache is now partitioned by current auth subject so stale seed/other-account widget data is not reused after real login. SQLite integrity IPC returns quick_check, journal mode, page/free counts, DB size, and WAL size.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>Installed-app long-run DB growth/recovery QA and restore-from-backup relaunch proof remain.</t>
+          <t>Installed-app long-run DB growth/recovery QA, restore-from-backup relaunch proof, and real-account cache rollover GUI QA remain.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; full cargo test --lib; settings cache check displays DB/WAL/pages/free details.</t>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; full cargo test --lib; npm.cmd run dev:widget:backend verifies real summary path remains green.</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/local_db.rs, src/lib/tauri/commands.ts, settings/page.tsx</t>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/widget/widget-summary-client.ts, src/lib/tauri/commands.ts</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>Cross-platform SQLite IPC change only; no macOS app/widget window logic touched.</t>
+          <t>Common SQLite/cache contract only; macOS window/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -3880,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4417,6 +4420,28 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Widget summary cache account boundary</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Local widget summary cache stores separate rows per auth subject and real-backend widget smoke still reads current server data successfully.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: real-backend smoke covers widget item state, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, and widget usage; widget summary cache is now partitioned by auth subject to avoid stale seed/other-account data. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: widget item controls now work with real item UUIDs when stateId is absent; real-backend smoke verifies state-id and task-id PATCH persistence, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1274,31 +1274,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; real-backend smoke now seeds widget_item_states and verifies PATCH /api/widget/items/{id}/state persists PINNED and CONFIRMED in PostgreSQL.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons now call /api/widget/items/{id}/state even when the server list only has the real item UUID, and real-backend smoke verifies task-id path fallback persists SNOOZED via backend find-or-create.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update the same backend item state without window flicker.</t>
+          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update backend state and refresh without window flicker.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies item-state PATCH plus DB persistence; cargo test --lib verifies local usage retry behavior.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; backend bootJar -x test compiles the compatible DTO/service path.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, scripts/dev-widget-real-backend.mjs, desktop-widget, widgetApi.ts, widget_usage.rs</t>
+          <t>#164 frontend, backend codex/widget-item-state-upsert-20260703, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget API contract only; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget API contract plus backend compatibility; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; real-backend smoke now seeds widget_item_states and verifies PATCH /api/widget/items/{id}/state persists PINNED and CONFIRMED in PostgreSQL.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons now call /api/widget/items/{id}/state even when the server list only has the real item UUID, and real-backend smoke verifies task-id path fallback persists SNOOZED via backend find-or-create.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update the same backend item state without window flicker.</t>
+          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update backend state and refresh without window flicker.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies item-state PATCH plus DB persistence; cargo test --lib verifies local usage retry behavior.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; backend bootJar -x test compiles the compatible DTO/service path.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164, scripts/dev-widget-real-backend.mjs, desktop-widget, widgetApi.ts, widget_usage.rs</t>
+          <t>#164 frontend, backend codex/widget-item-state-upsert-20260703, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget API contract only; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget API contract plus backend compatibility; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4442,6 +4442,28 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state item-id fallback</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend against backend branch codex/widget-item-state-upsert-20260703</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Desktop-widget shaped PATCH using the task item UUID path persists SNOOZED in widget_item_states when no stateId is present in the UI row.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget item controls now work with real item UUIDs when stateId is absent; real-backend smoke verifies state-id and task-id PATCH persistence, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: widget item controls work with real item UUIDs and apply successful state changes immediately in the widget session; real-backend smoke verifies state-id and task-id PATCH persistence, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1274,31 +1274,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons now call /api/widget/items/{id}/state even when the server list only has the real item UUID, and real-backend smoke verifies task-id path fallback persists SNOOZED via backend find-or-create.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback and now apply successful CONFIRMED/HIDDEN/SNOOZED/PINNED actions immediately in the widget session so server refresh does not re-show handled rows.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update backend state and refresh without window flicker.</t>
+          <t>Manual Windows GUI QA still remains for mouse click feedback across all bubble types and for persistence after backend starts returning item-state-aware lists.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; backend bootJar -x test compiles the compatible DTO/service path.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; npm.cmd run typecheck verifies the UI override path.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164 frontend, backend codex/widget-item-state-upsert-20260703, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget API contract plus backend compatibility; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons now call /api/widget/items/{id}/state even when the server list only has the real item UUID, and real-backend smoke verifies task-id path fallback persists SNOOZED via backend find-or-create.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback and now apply successful CONFIRMED/HIDDEN/SNOOZED/PINNED actions immediately in the widget session so server refresh does not re-show handled rows.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Desktop GUI QA for each bubble item control remains: confirm/pin/hide/snooze should update backend state and refresh without window flicker.</t>
+          <t>Manual Windows GUI QA still remains for mouse click feedback across all bubble types and for persistence after backend starts returning item-state-aware lists.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; backend bootJar -x test compiles the compatible DTO/service path.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; npm.cmd run typecheck verifies the UI override path.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164 frontend, backend codex/widget-item-state-upsert-20260703, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget API contract plus backend compatibility; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4464,6 +4464,28 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state optimistic UI</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>After successful item-state PATCH, desktop widget removes confirmed/hidden/snoozed rows or pins rows locally and keeps the override across the next refresh cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget item controls work with real item UUIDs and apply successful state changes immediately in the widget session; real-backend smoke verifies state-id and task-id PATCH persistence, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-03 Windows: widget item controls work with real item UUIDs, apply successful state changes immediately, and reload persisted item states from /api/widget/items/states; real-backend smoke verifies state-id and task-id PATCH, item-state readback, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1274,31 +1274,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback and now apply successful CONFIRMED/HIDDEN/SNOOZED/PINNED actions immediately in the widget session so server refresh does not re-show handled rows.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback, then reload persisted item states through /api/widget/items/states so CONFIRMED/HIDDEN/SNOOZED/PINNED survives refresh/reopen instead of only the current click session.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Manual Windows GUI QA still remains for mouse click feedback across all bubble types and for persistence after backend starts returning item-state-aware lists.</t>
+          <t>Manual Windows GUI QA still remains for visual click feedback and backend-side filtering once item-state-aware domain lists are expanded beyond widget state lookup.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; npm.cmd run typecheck verifies the UI override path.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164 frontend, backend #183, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, widgetApi.ts, dev-widget-real-backend.mjs, WidgetService.java, WidgetItemStateResponse.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget behavior; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback and now apply successful CONFIRMED/HIDDEN/SNOOZED/PINNED actions immediately in the widget session so server refresh does not re-show handled rows.</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback, then reload persisted item states through /api/widget/items/states so CONFIRMED/HIDDEN/SNOOZED/PINNED survives refresh/reopen instead of only the current click session.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Manual Windows GUI QA still remains for mouse click feedback across all bubble types and for persistence after backend starts returning item-state-aware lists.</t>
+          <t>Manual Windows GUI QA still remains for visual click feedback and backend-side filtering once item-state-aware domain lists are expanded beyond widget state lookup.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH plus task-id fallback PATCH and DB persistence; npm.cmd run typecheck verifies the UI override path.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>#164 frontend, backend #183, desktop-widget/page.tsx, dev-widget-real-backend.mjs, WidgetService.java</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, widgetApi.ts, dev-widget-real-backend.mjs, WidgetService.java, WidgetItemStateResponse.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget behavior; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4486,6 +4486,28 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state readback</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend against backend #183 branch</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>After task-id fallback PATCH persists SNOOZED, GET /api/widget/items/states returns the same state and desktop widget applies persisted states during data load.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +83,46 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009FD3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008FD59D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -110,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,6 +176,58 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,12 +767,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>주의</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Mac 수정 병합 후 Windows에서만 재검증. 앞으로 Windows 작업 중 macOS 전용 로직은 건드리지 않는 방향.</t>
+          <t>최근 갱신</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-03 Windows: widget item controls work with real item UUIDs, apply successful state changes immediately, and reload persisted item states from /api/widget/items/states; real-backend smoke verifies state-id and task-id PATCH, item-state readback, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -698,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -781,7 +873,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -831,7 +923,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -878,35 +970,35 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지는 바 복원 항목 시드(#162)</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 Windows 실사용 확인</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close/flicker regression QA remains.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>#162</t>
+          <t>#164, authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>창 다중 오픈/깜빡임 재발 확인</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -928,35 +1020,35 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>열기/닫기/최소화/복원/항상 위/고스트/위치 저장</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; Windows/non-mac existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>투명창, 무테두리, 그림자 GUI QA</t>
+          <t>Transparent frameless shadow and no-scrollbar GUI capture QA.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>창 테두리 없음, 스크롤바 없음, 드래그 가능</t>
+          <t>cargo test --lib; actual Windows Tauri screen capture must show no border/scrollbar/titlebar flicker.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>src-tauri/src/lib.rs, desktop-widget</t>
+          <t>#164, src-tauri/src/lib.rs, desktop-widget</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView shadow/transparent 확인</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS async build path preserved.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -976,40 +1068,40 @@
           <t>SQLite</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>꽤 됨</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>bundled rusqlite, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>실앱 장시간 DB 무결성/복구 QA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>quick_check, 백업/복구, 재시작 유지</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>local_db.rs</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>현재 단위테스트 기준만 강함</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. Widget summary cache is now partitioned by current auth subject so stale seed/other-account widget data is not reused after real login. SQLite integrity IPC returns quick_check, journal mode, page/free counts, DB size, and WAL size.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Installed-app long-run DB growth/recovery QA, restore-from-backup relaunch proof, and real-account cache rollover GUI QA remain.</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; full cargo test --lib; npm.cmd run dev:widget:backend verifies real summary path remains green.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/widget/widget-summary-client.ts, src/lib/tauri/commands.ts</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Common SQLite/cache contract only; macOS window/runtime logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -1026,90 +1118,90 @@
           <t>로컬 폴더 트래킹</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>폴더 등록, scan, native watch, FTS 검색, 미리보기, 열기, reindex</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>대용량/삭제/권한/장시간 watch QA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제가 local_file_events에 반영</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>local_files.rs</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Windows notify 경로 확인</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Real Tauri GUI long-run watch QA, large file/permission-denied cases, and SQLite row inspection in an installed app profile.</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_files.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>로컬 파일 서버 동기화</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>승인 이벤트를 /api/local-file-events/sync로 전송</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>localEventId 매칭 PR #158 머지와 실백엔드 왕복</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>sync 후 올바른 이벤트가 SYNCED/FAILED</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>#158</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>현재 체크아웃에는 #158 미포함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>GUI watch/outbox long-run QA, SQLite row state inspection, and large/permission-denied file cases still remain.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts, localFileAnalysisApi.ts</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -1128,35 +1220,35 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>60</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground window/process 감지, 동의 기반 30초 자동 캡처</t>
+          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>실사용 dwell time 검증</t>
+          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>앱 전환 시 appName/windowTitle 기록, /api/activity/today 반영</t>
+          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>activity.rs, activity-client.ts</t>
+          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows 전용 로직 유지</t>
+          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1178,35 +1270,35 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>75</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>로컬 상세 이벤트, rollup, 서버 usage summary 동기화</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback, then reload persisted item states through /api/widget/items/states so CONFIRMED/HIDDEN/SNOOZED/PINNED survives refresh/reopen instead of only the current click session.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>실서버 settings 매칭 실패 케이스 QA</t>
+          <t>Manual Windows GUI QA still remains for visual click feedback and backend-side filtering once item-state-aware domain lists are expanded beyond widget state lookup.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>위젯 조작 후 rollup sync</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>widget_usage.rs</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, widgetApi.ts, dev-widget-real-backend.mjs, WidgetService.java, WidgetItemStateResponse.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>장시간 동기화 확인</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1228,35 +1320,35 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>채팅방/메시지 API, 전송, 읽음, 로컬 메시지 캐시, LiveKit 진입 코드</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>실채팅/음성 연결 QA</t>
+          <t>LiveKit in-app audio GUI/mic permission QA and token-backed room join still need live desktop verification.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>메시지 전송/읽음/캐시, 음성방 토큰</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>desktop-widget/page.tsx</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, widgetDisplayApi.ts, desktop-widget/page.tsx</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>마이크 권한 확인</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1281,7 +1373,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1331,7 +1423,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="26" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1381,7 +1473,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="26" t="n">
         <v>60</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1431,7 +1523,7 @@
           <t>문제</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="26" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1481,7 +1573,7 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="26" t="n">
         <v>40</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1531,7 +1623,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1581,7 +1673,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="26" t="n">
         <v>60</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1631,7 +1723,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1681,7 +1773,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1731,7 +1823,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1781,7 +1873,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="26" t="n">
         <v>55</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1831,7 +1923,7 @@
           <t>검증필요</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="26" t="n">
         <v>65</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1862,6 +1954,106 @@
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Mac 팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>실시간 활동 추적</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Full settings GUI toggle QA in real Tauri session remains.</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>#164, settingsApi.ts, settings.ts, settings/page.tsx, privacy-consent-panel.tsx, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
         </is>
       </c>
     </row>
@@ -1885,6 +2077,60 @@
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
       <formula>60</formula>
     </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D24">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -1899,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1982,7 +2228,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2032,7 +2278,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2079,35 +2325,35 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>bar+todo 표시, 나머지는 바 복원 항목 시드(#162)</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 Windows 실사용 확인</t>
+          <t>Real OAuth Windows GUI relaunch/minimize/close/flicker regression QA remains.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>로그인 후 bar/todo 표시, 각 위젯 복원</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>#162</t>
+          <t>#164, authenticated-surfaces.ts, src-tauri/src/lib.rs</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>창 다중 오픈/깜빡임 재발 확인</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2129,35 +2375,35 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>열기/닫기/최소화/복원/항상 위/고스트/위치 저장</t>
+          <t>Open/close/minimize/restore/topmost/ghost/position store; Windows/non-mac existing windows now reapply saved preferred-monitor position and close-all/context persist immediately.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>투명창, 무테두리, 그림자 GUI QA</t>
+          <t>Transparent frameless shadow and no-scrollbar GUI capture QA.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>창 테두리 없음, 스크롤바 없음, 드래그 가능</t>
+          <t>cargo test --lib; actual Windows Tauri screen capture must show no border/scrollbar/titlebar flicker.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>src-tauri/src/lib.rs, desktop-widget</t>
+          <t>#164, src-tauri/src/lib.rs, desktop-widget</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Windows WebView shadow/transparent 확인</t>
+          <t>Windows WebView transparent/shadow QA still required; macOS async build path preserved.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2177,40 +2423,40 @@
           <t>SQLite</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>꽤 됨</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>bundled rusqlite, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>실앱 장시간 DB 무결성/복구 QA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>quick_check, 백업/복구, 재시작 유지</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>local_db.rs</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>현재 단위테스트 기준만 강함</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Bundled rusqlite, WAL, auth/room/folder/file/FTS/outbox/widget/activity/timer/cache/backup. Widget summary cache is now partitioned by current auth subject so stale seed/other-account widget data is not reused after real login. SQLite integrity IPC returns quick_check, journal mode, page/free counts, DB size, and WAL size.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Installed-app long-run DB growth/recovery QA, restore-from-backup relaunch proof, and real-account cache rollover GUI QA remain.</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; full cargo test --lib; npm.cmd run dev:widget:backend verifies real summary path remains green.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_db.rs, src/lib/widget/widget-summary-client.ts, src/lib/tauri/commands.ts</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Common SQLite/cache contract only; macOS window/runtime logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2227,90 +2473,90 @@
           <t>로컬 폴더 트래킹</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>폴더 등록, scan, native watch, FTS 검색, 미리보기, 열기, reindex</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>대용량/삭제/권한/장시간 watch QA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제가 local_file_events에 반영</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>local_files.rs</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Windows notify 경로 확인</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Real Tauri GUI long-run watch QA, large file/permission-denied cases, and SQLite row inspection in an installed app profile.</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/local_files.rs, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>로컬 파일 서버 동기화</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>승인 이벤트를 /api/local-file-events/sync로 전송</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>localEventId 매칭 PR #158 머지와 실백엔드 왕복</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>sync 후 올바른 이벤트가 SYNCED/FAILED</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>#158</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>현재 체크아웃에는 #158 미포함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>GUI watch/outbox long-run QA, SQLite row state inspection, and large/permission-denied file cases still remain.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>#164, scripts/dev-widget-real-backend.mjs, managed-folder-client.ts, localFileAnalysisApi.ts</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2329,35 +2575,35 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>60</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground window/process 감지, 동의 기반 30초 자동 캡처</t>
+          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>실사용 dwell time 검증</t>
+          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>앱 전환 시 appName/windowTitle 기록, /api/activity/today 반영</t>
+          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>activity.rs, activity-client.ts</t>
+          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows 전용 로직 유지</t>
+          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2379,35 +2625,35 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>75</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>로컬 상세 이벤트, rollup, 서버 usage summary 동기화</t>
+          <t>Widget display uses server-first summary fallback; usage rollups mark failed/mismatched sync attempts in SQLite for retry; desktop widget item buttons call /api/widget/items/{id}/state with real item UUID fallback, then reload persisted item states through /api/widget/items/states so CONFIRMED/HIDDEN/SNOOZED/PINNED survives refresh/reopen instead of only the current click session.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>실서버 settings 매칭 실패 케이스 QA</t>
+          <t>Manual Windows GUI QA still remains for visual click feedback and backend-side filtering once item-state-aware domain lists are expanded beyond widget state lookup.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>위젯 조작 후 rollup sync</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>widget_usage.rs</t>
+          <t>#164 frontend, backend #183, desktop-widget/page.tsx, widgetApi.ts, dev-widget-real-backend.mjs, WidgetService.java, WidgetItemStateResponse.java</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>장시간 동기화 확인</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2429,35 +2675,35 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>65</v>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>채팅방/메시지 API, 전송, 읽음, 로컬 메시지 캐시, LiveKit 진입 코드</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>실채팅/음성 연결 QA</t>
+          <t>LiveKit in-app audio GUI/mic permission QA and token-backed room join still need live desktop verification.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>메시지 전송/읽음/캐시, 음성방 토큰</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>desktop-widget/page.tsx</t>
+          <t>#164, scripts/dev-widget-real-backend.mjs, widgetDisplayApi.ts, desktop-widget/page.tsx</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>마이크 권한 확인</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2482,7 +2728,7 @@
           <t>진행</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="17" t="n">
         <v>75</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2511,6 +2757,106 @@
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>실시간 활동 추적</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Codex Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Full settings GUI toggle QA in real Tauri session remains.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>#164, settingsApi.ts, settings.ts, settings/page.tsx, privacy-consent-panel.tsx, scripts/dev-widget-real-backend.mjs</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>Codex Windows</t>
         </is>
@@ -2535,6 +2881,60 @@
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
       <formula>60</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D14">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F4CCCC"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3201,7 +3601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3417,22 +3817,54 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>로컬 파일/활동/SQLite 실백엔드 왕복</t>
+          <t>Local file/activity/SQLite real-backend and GUI QA follow-up</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SQLite 상태와 서버 응답 일치</t>
+          <t>API smoke passes; GUI SQLite/watch/runtime evidence captured separately</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>실백엔드 + Docker 환경</t>
+          <t>npm.cmd run dev:widget:backend + Tauri GUI QA</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>#158 병합 여부 확인</t>
+          <t>Do not modify macOS-specific logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Windows widget window runtime stabilization GUI QA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>No delayed wave/flicker after login; preferred monitor move reapplies to visible widgets; close-all leaves no widget windows.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>npm.cmd run tauri:dev:backend + Windows screen capture; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Do not touch macOS-specific widget/app logic.</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3593,24 +4025,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>로컬 폴더</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>테스트 폴더 watch</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>생성/수정/삭제 반영</t>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; test folder watch in Tauri GUI</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>CREATED/UPDATED/DELETED events plus FTS add/remove; GUI watch reflects created/modified/deleted files</t>
         </is>
       </c>
     </row>
@@ -3677,6 +4109,402 @@
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>생성/수정/삭제 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Real backend API smoke</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>widget, chat, local-file sync, activity, summaries pass against Docker/backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Widget launch failure retry</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Code path + typecheck + tauri-boundaries</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>All-open failure leaves launched flag false and avoids starting background runtimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Desktop widget summary fallback</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Backend summary extended fields are typed and can populate widget display fallback/cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Widget usage rollup retry</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cd src-tauri; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Failed or unmatched usage rollups are marked FAILED in SQLite and remain retry candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Widget window runtime stabilization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cd src-tauri; cargo test --lib; npm.cmd run dev:widget:backend; then Windows Tauri GUI smoke</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Windows/non-mac open_widget_window waits for real window creation; existing widgets move with preferred monitor; room context/close-all persist; macOS async build path preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Widget communication voice smoke</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Real backend verifies voice room create/read/mic/leave; token shape is checked when local LiveKit secret allows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>로컬 파일 분석 서버 왕복</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>/api/local-file-events/sync CREATED returns resourceId, UPDATED preserves it, then /api/local-file-analyses returns ANALYZE_RESOURCE job before DELETE cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>활동 추적 서버 생성/삭제 왕복</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>POST /api/activity/current-app creates a room-scoped record, GET /api/activity/today includes it, DELETE /api/activity/{id} removes it, and /today no longer returns it</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Privacy consent API contract</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Frontend adapter typechecks; smoke asserts GET /api/me/privacy-consents contains ACTIVITY_CONTEXT and MANAGED_FOLDER, PATCH disables/enables MANAGED_FOLDER, then local file sync proceeds with consent re-enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Windows foreground activity capture</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Windows-only test windows_foreground_capture_returns_app_name calls Win32 foreground capture and asserts non-empty app name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>SQLite ??</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::sqlite_integrity_result_includes_storage_diagnostics; settings cache check in Tauri app</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>quick_check ok plus DB/WAL byte sizes, page count, free page count, and journal mode visible from IPC/UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>?? ?? flush</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend; manual Tauri logout/app-close QA</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>On authenticated surface stop, final incremental activity capture and pending buffer sync are attempted before local auto-capture state resets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>??? ???? ??</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend; cargo test --lib local_db::tests::records_and_recovers_running_timer_state</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Start WORK timer in seeded room, dashboard/widget summary expose runningTimer, heartbeat/pause/resume/stop succeed, local recovery test remains green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state API</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Seeded TODO task item state changes to PINNED then CONFIRMED through /api/widget/items/{id}/state and PostgreSQL confirms persistence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Widget summary cache account boundary</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>cargo test --lib local_db::tests::widget_summary_cache_is_partitioned_by_cache_key; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Local widget summary cache stores separate rows per auth subject and real-backend widget smoke still reads current server data successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state item-id fallback</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend against backend branch codex/widget-item-state-upsert-20260703</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Desktop-widget shaped PATCH using the task item UUID path persists SNOOZED in widget_item_states when no stateId is present in the UI row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state optimistic UI</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>After successful item-state PATCH, desktop widget removes confirmed/hidden/snoozed rows or pins rows locally and keeps the override across the next refresh cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Widget item state readback</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>npm.cmd run dev:widget:backend against backend #183 branch</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>After task-id fallback PATCH persists SNOOZED, GET /api/widget/items/states returns the same state and desktop widget applies persisted states during data load.</t>
         </is>
       </c>
     </row>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget item controls work with real item UUIDs, apply successful state changes immediately, and reload persisted item states from /api/widget/items/states; real-backend smoke verifies state-id and task-id PATCH, item-state readback, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: activity auto-capture now honors Settings privacy consent changes immediately. Disabling activity detection stops the auto-capture interval and resets incremental checkpoints without waiting for the previous 60s consent cache; validation passed typecheck, Tauri boundary, and product-rule checks. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1223,32 +1223,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>65</v>
+      <c r="D9" s="17" t="n">
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
+          <t>Actual Windows GUI foreground-switch dwell QA, in-flight revoke edge proof, and long-run retry/outbox observation remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, settings/page.tsx, activity-client.ts, src-tauri/src/activity.rs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1974,31 +1974,31 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains.</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+          <t>Real Windows installed-app GUI session with app switching, disable/re-enable, relaunch, and server today-activity readback still needs capture evidence.</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows.</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, authenticated-surfaces.ts, settings/page.tsx</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+          <t>No macOS-specific runtime/window code changed.</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
@@ -2578,32 +2578,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>65</v>
+      <c r="D9" s="17" t="n">
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
+          <t>Actual Windows GUI foreground-switch dwell QA, in-flight revoke edge proof, and long-run retry/outbox observation remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, settings/page.tsx, activity-client.ts, src-tauri/src/activity.rs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2779,31 +2779,31 @@
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+          <t>Real Windows installed-app GUI session with app switching, disable/re-enable, relaunch, and server today-activity readback still needs capture evidence.</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows.</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, authenticated-surfaces.ts, settings/page.tsx</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+          <t>No macOS-specific runtime/window code changed.</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4508,6 +4508,28 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Activity consent revocation immediate stop</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Settings activityDetectionEnabled save success -&gt; auto-capture cache invalidation; npm.cmd run typecheck/check:tauri-boundaries/check:product-rules</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>After consent OFF, the next 30s automatic capture is stopped and the incremental checkpoint is reset. Long-run GUI evidence remains follow-up QA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-04 Windows: activity auto-capture now honors Settings privacy consent changes immediately. Disabling activity detection stops the auto-capture interval and resets incremental checkpoints without waiting for the previous 60s consent cache; validation passed typecheck, Tauri boundary, and product-rule checks. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: activity auto-capture now honors Settings privacy consent changes immediately; the unused legacy tauri/activity-runtime.ts poller was removed so authenticated-surfaces uses one automatic capture path; activity record diagnostics now report record_activity_context. Validation passed typecheck, lint, Tauri boundary, product-rule checks, and cargo test --lib. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window. Removed the unused legacy tauri/activity-runtime.ts poller so the authenticated-surface activity-auto-capture runtime remains the single automatic capture path.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains. Activity record adapter diagnostics now use record_activity_context instead of read_activity_context for clearer failure evidence.</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window. Removed the unused legacy tauri/activity-runtime.ts poller so the authenticated-surface activity-auto-capture runtime remains the single automatic capture path.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains. Activity record adapter diagnostics now use record_activity_context instead of read_activity_context for clearer failure evidence.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4530,6 +4530,28 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Single automatic activity runtime</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rg activity-runtime/startTauriActivityRuntime; npm.cmd run typecheck/check:tauri-boundaries/check:product-rules/lint; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Only activity-auto-capture is launched from authenticated-surfaces; no unused legacy activity runtime remains.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-04 Windows: activity auto-capture now honors Settings privacy consent changes immediately; the unused legacy tauri/activity-runtime.ts poller was removed so authenticated-surfaces uses one automatic capture path; activity record diagnostics now report record_activity_context. Validation passed typecheck, lint, Tauri boundary, product-rule checks, and cargo test --lib. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: PR #167 activity runtime hardening is CI-clean. Real-backend smoke against backend branch codex/widget-item-state-upsert-20260703 passed widget summary/settings/context/item-state readback, chat send/read, voice room CRUD except optional LiveKit token, timer lifecycle, widget usage summary, local-file sync CREATED/UPDATED/DELETED, local-file analysis job, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Backend process was stopped after verification. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>No macOS-specific runtime/window code changed.</t>
+          <t>No macOS-specific runtime/window code changed. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>No macOS-specific runtime/window code changed.</t>
+          <t>No macOS-specific runtime/window code changed. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4552,6 +4552,28 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Real backend smoke after activity runtime hardening</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NEXT_PUBLIC_API_BASE_URL=http://localhost:8080; JWT_SECRET=local-development-jwt-secret-key-32-bytes-minimum; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Passed widget, chat, timer, local-file, activity, daily summary, generated document, and room memory smoke. Voice token endpoint returned HTTP 500 and was optional-skipped.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-03 Windows: widget item controls work with real item UUIDs, apply successful state changes immediately, and reload persisted item states from /api/widget/items/states; real-backend smoke verifies state-id and task-id PATCH, item-state readback, timer lifecycle, activity/current-app, local-file sync/analysis, privacy consent, widget usage, and account-partitioned widget summary cache. macOS app/widget logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: PR #167 activity runtime hardening is CI-clean. Real-backend smoke against backend branch codex/widget-item-state-upsert-20260703 passed widget summary/settings/context/item-state readback, chat send/read, voice room CRUD except optional LiveKit token, timer lifecycle, widget usage summary, local-file sync CREATED/UPDATED/DELETED, local-file analysis job, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Backend process was stopped after verification. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -1223,32 +1223,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>65</v>
+      <c r="D9" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window. Removed the unused legacy tauri/activity-runtime.ts poller so the authenticated-surface activity-auto-capture runtime remains the single automatic capture path.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
+          <t>Actual Windows GUI foreground-switch dwell QA, in-flight revoke edge proof, and long-run retry/outbox observation remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, settings/page.tsx, activity-client.ts, src-tauri/src/activity.rs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1974,31 +1974,31 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains. Activity record adapter diagnostics now use record_activity_context instead of read_activity_context for clearer failure evidence.</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+          <t>Real Windows installed-app GUI session with app switching, disable/re-enable, relaunch, and server today-activity readback still needs capture evidence.</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, authenticated-surfaces.ts, settings/page.tsx</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+          <t>No macOS-specific runtime/window code changed. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -2578,32 +2578,32 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>65</v>
+      <c r="D9" s="17" t="n">
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Win32 capture path remains; activity buffer resend now preserves consent and smoke records /api/activity/current-app.</t>
+          <t>Win32 foreground app capture and local/server sync path remain in place. Activity consent changes from Settings now invalidate the auto-capture consent cache immediately; disabling activity detection stops the interval and resets incremental checkpoints without waiting for the previous 60s refresh window. Removed the unused legacy tauri/activity-runtime.ts poller so the authenticated-surface activity-auto-capture runtime remains the single automatic capture path.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Real Tauri foreground-window dwell QA and long-run retry behavior still remain.</t>
+          <t>Actual Windows GUI foreground-switch dwell QA, in-flight revoke edge proof, and long-run retry/outbox observation remain.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>dev:widget:backend records smoke activity and verifies /api/activity/today contains it.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; manual Tauri GUI QA should toggle activity consent off and confirm no further auto-capture after save. rg confirms no legacy activity-runtime references remain. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>#164, activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, settings/page.tsx, activity-client.ts, src-tauri/src/activity.rs</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Do not touch macOS activity cfg; Mac team owns macOS widget/app fix.</t>
+          <t>Windows/common consent runtime only; macOS activity implementation remains Mac-team owned and untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2779,31 +2779,31 @@
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Windows foreground app/window capture uses Win32 APIs, stores dwell in Tauri SQLite buffer, reflects consented records to /api/activity/current-app, verifies /today inclusion/delete, and now has a Windows-only real foreground capture unit test.</t>
+          <t>Automatic incremental activity capture is gated by server privacy consent and now reacts immediately when the Settings privacy toggle changes. Existing login-time start and logout/close flush behavior remains. Activity record adapter diagnostics now use record_activity_context instead of read_activity_context for clearer failure evidence.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Long-running incremental capture and settings/permission UX QA in real Windows Tauri GUI remain.</t>
+          <t>Real Windows installed-app GUI session with app switching, disable/re-enable, relaunch, and server today-activity readback still needs capture evidence.</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>cargo test --lib on Windows includes windows_foreground_capture_returns_app_name; npm.cmd run dev:widget:backend verifies server record/today/delete.</t>
+          <t>npm.cmd run typecheck; npm.cmd run check:tauri-boundaries; npm.cmd run check:product-rules; follow-up GUI QA: login, enable, switch app, disable, wait beyond one interval, verify no new activity rows. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>#164, src-tauri/src/activity.rs, src/lib/local/activity-client.ts, scripts/dev-widget-real-backend.mjs</t>
+          <t>activity-auto-capture.ts, authenticated-surfaces.ts, settings/page.tsx</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Windows-only test; macOS osascript/permission path is untouched and remains Mac-team owned.</t>
+          <t>No macOS-specific runtime/window code changed. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4508,6 +4508,72 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Activity consent revocation immediate stop</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Settings activityDetectionEnabled save success -&gt; auto-capture cache invalidation; npm.cmd run typecheck/check:tauri-boundaries/check:product-rules</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>After consent OFF, the next 30s automatic capture is stopped and the incremental checkpoint is reset. Long-run GUI evidence remains follow-up QA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Single automatic activity runtime</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rg activity-runtime/startTauriActivityRuntime; npm.cmd run typecheck/check:tauri-boundaries/check:product-rules/lint; cargo test --lib</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Only activity-auto-capture is launched from authenticated-surfaces; no unused legacy activity runtime remains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Real backend smoke after activity runtime hardening</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NEXT_PUBLIC_API_BASE_URL=http://localhost:8080; JWT_SECRET=local-development-jwt-secret-key-32-bytes-minimum; npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Passed widget, chat, timer, local-file, activity, daily summary, generated document, and room memory smoke. Voice token endpoint returned HTTP 500 and was optional-skipped.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-04 Windows: PR #167 activity runtime hardening is CI-clean. Real-backend smoke against backend branch codex/widget-item-state-upsert-20260703 passed widget summary/settings/context/item-state readback, chat send/read, voice room CRUD except optional LiveKit token, timer lifecycle, widget usage summary, local-file sync CREATED/UPDATED/DELETED, local-file analysis job, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Backend process was stopped after verification. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows/backend: local LiveKit server-only defaults were added to backend application-local.yml, and frontend real-backend smoke now requires /api/voice/rooms/{id}/token with voiceRoomId, participantId, serverUrl, token, and expiresAt. Full smoke passes without optional LiveKit skip. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -1273,8 +1273,8 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>90</v>
+      <c r="D10" s="17" t="n">
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application. 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched. Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>재시작 후 running timer recover</t>
+          <t>재시작 후 running timer recover 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>장시간 heartbeat 확인</t>
+          <t>장시간 heartbeat 확인 Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2628,8 +2628,8 @@
           <t>progress</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>90</v>
+      <c r="D10" s="17" t="n">
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application.</t>
+          <t>npm.cmd run dev:widget:backend verifies state-id PATCH, task-id fallback PATCH, /api/widget/items/states readback, and DB persistence; npm.cmd run typecheck verifies frontend state application. 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched.</t>
+          <t>Windows/Tauri widget behavior plus backend widget API; macOS app/widget runtime remains Mac-team owned and untouched. Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>재시작 후 running timer recover</t>
+          <t>재시작 후 running timer recover 2026-07-04 smoke now requires /api/voice/rooms/{id}/token and verifies voiceRoomId, participantId, serverUrl, token, and expiresAt.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>장시간 heartbeat 확인</t>
+          <t>장시간 heartbeat 확인 Backend local profile now has server-only LiveKit development defaults; no LiveKit key/secret is placed in the frontend.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4574,6 +4574,28 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Voice token real-backend smoke required</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Backend local profile bootRun + NEXT_PUBLIC_API_BASE_URL=http://localhost:8080 npm.cmd run dev:widget:backend</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Passed /api/voice/rooms/{id}/token with voiceRoomId, participantId, serverUrl, token, and expiresAt; no optional LiveKit skip remains.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-04 Windows: PR #167 activity runtime hardening is CI-clean. Real-backend smoke against backend branch codex/widget-item-state-upsert-20260703 passed widget summary/settings/context/item-state readback, chat send/read, voice room CRUD except optional LiveKit token, timer lifecycle, widget usage summary, local-file sync CREATED/UPDATED/DELETED, local-file analysis job, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Backend process was stopped after verification. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: Tauri GUI smoke launched real backend dev app; main Bubli window was visible and widget windows were created. Widget display room propagation was hardened: room mode uses /api/project-rooms/{roomId}/tasks, room schedules beat dashboard schedules, non-matching running timers are hidden, and all bubble payloads carry roomId. Real backend seed confirmed room task count 6 vs dashboard task count 2. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
         </is>
       </c>
     </row>
@@ -874,11 +874,11 @@
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>WebView /app, 로그인 세션 복구, 주 모니터 위치 조정, 종료 시 위젯 종료 로직</t>
+          <t>WebView /app, 로그인 세션 복구, 주 모니터 위치 조정, 종료 시 위젯 종료 로직 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>앱 실행, 로그인 화면, 주 모니터 위치 확인</t>
+          <t>앱 실행, 로그인 화면, 주 모니터 위치 확인 Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 재검증</t>
+          <t>Mac 수정 병합 후 재검증 Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -974,11 +974,11 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn. 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required. Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix. Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1324,11 +1324,11 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId. 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>시작/정지/일시정지/재개/heartbeat, 로컬 복구</t>
+          <t>시작/정지/일시정지/재개/heartbeat, 로컬 복구 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>재시작 후 running timer recover</t>
+          <t>재시작 후 running timer recover Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>장시간 heartbeat 확인</t>
+          <t>장시간 heartbeat 확인 Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2229,11 +2229,11 @@
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>WebView /app, 로그인 세션 복구, 주 모니터 위치 조정, 종료 시 위젯 종료 로직</t>
+          <t>WebView /app, 로그인 세션 복구, 주 모니터 위치 조정, 종료 시 위젯 종료 로직 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>앱 실행, 로그인 화면, 주 모니터 위치 확인</t>
+          <t>앱 실행, 로그인 화면, 주 모니터 위치 확인 Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Mac 수정 병합 후 재검증</t>
+          <t>Mac 수정 병합 후 재검증 Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2329,11 +2329,11 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn.</t>
+          <t>Login opens bar + primary widget after auth; Windows/non-mac widget open command now returns after actual Tauri window creation instead of delayed background spawn. 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required.</t>
+          <t>cargo fmt/check/tests, real-backend smoke, and PR CI; GUI capture still required. Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix.</t>
+          <t>macOS keeps the previous async widget build path; Mac team owns Mac widget fix. Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2679,11 +2679,11 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId.</t>
+          <t>Chat rooms/messages/read cache plus voice room create/read/mic/leave are connected in the real-backend widget smoke; widget voice type now accepts createdByUserId. 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend verifies chat and voice HTTP roundtrips; GUI voice join still required. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Token smoke is optional when local LiveKit secret is unavailable; Mac-specific logic untouched. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2729,11 +2729,11 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>시작/정지/일시정지/재개/heartbeat, 로컬 복구</t>
+          <t>시작/정지/일시정지/재개/heartbeat, 로컬 복구 2026-07-04 room propagation display patch: desktop widgets now fetch TODO from /api/project-rooms/{roomId}/tasks in room mode, prefer room-scoped schedules over dashboard schedules, hide non-matching running timers, and carry roomId on all bubble payloads.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>재시작 후 running timer recover</t>
+          <t>재시작 후 running timer recover Verified with typecheck/product-rules/tauri-boundaries and real backend seed: project-room task API returned 6 room tasks while dashboard tasks returned 2.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>장시간 heartbeat 확인</t>
+          <t>장시간 heartbeat 확인 Mac runtime/window paths untouched; patch is frontend widget display/API only.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4574,6 +4574,28 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Desktop widget room-scoped display data</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run check:product-rules; npm.cmd run check:tauri-boundaries; backend local bootRun + seed + GET /api/project-rooms/{roomId}/tasks</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Room task API returned 6 seeded room tasks while dashboard task API returned 2; widget display now uses room-scoped task/schedule/timer data when selectedRoomId exists.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
+++ b/docs/tauri-widget-platform-split-checklist-2026-07-03.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>2026-07-04 Windows: PR #167 activity runtime hardening is CI-clean. Real-backend smoke against backend branch codex/widget-item-state-upsert-20260703 passed widget summary/settings/context/item-state readback, chat send/read, voice room CRUD except optional LiveKit token, timer lifecycle, widget usage summary, local-file sync CREATED/UPDATED/DELETED, local-file analysis job, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Backend process was stopped after verification. macOS app/widget/runtime logic remains Mac-team owned and untouched.</t>
+          <t>2026-07-04 Windows: managed-folder auto-sync now honors Settings localFolderEnabled changes immediately. Disabling local folder consent stops the interval, clears pending sync work, detaches watch listeners, and calls unwatchAllManagedFolders without waiting for the old 60s consent cache. Validation passed typecheck/product-rules/tauri-boundaries and targeted local_files/SQLite cargo tests. macOS native watch logic remains untouched.</t>
         </is>
       </c>
     </row>
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -1174,11 +1174,11 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -2024,11 +2024,11 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J25" s="18" t="inlineStr">
@@ -2479,11 +2479,11 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout.</t>
+          <t>Folder register/scan/native watch/FTS/preview/open/reindex. Direct watch callback test now verifies CREATED -&gt; UPDATED -&gt; DELETED plus FTS add/remove on Windows checkout. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke.</t>
+          <t>cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete; full cargo test --lib; real-backend local file smoke. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched.</t>
+          <t>Windows evidence only; macOS FSEvents/app-widget logic remains Mac-team owned and untouched. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -2529,11 +2529,11 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job.</t>
+          <t>Approved local file CREATED/UPDATED/DELETED sync is smoke-tested. Created PERSONAL resource then posts extracted text/key sentences to /api/local-file-analyses to create an ANALYZE_RESOURCE job. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries.</t>
+          <t>npm.cmd run dev:widget:backend checks /api/local-file-events/sync CREATED/UPDATED/DELETED plus /api/local-file-analyses before cleanup. 2026-07-04 real-backend smoke passed for widget summary/settings/context/item-state, chat send/read, timer lifecycle, widget usage, local-file sync/analysis, activity current-app/today/delete, daily summaries, generated document export, and room memory summaries. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up.</t>
+          <t>Windows-only verification scope; macOS widget/app path remains Mac-team owned. Voice token endpoint returned HTTP 500 and was optional-skipped by the smoke script; LiveKit token remains backend/config follow-up. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -2829,11 +2829,11 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types.</t>
+          <t>Frontend settings adapter now maps backend /api/me/privacy-consents {items:[ACTIVITY_CONTEXT, MANAGED_FOLDER]} to app booleans and PATCHes only backend-supported consent types. 2026-07-04 managed-folder consent runtime patch: Settings localFolderEnabled save now immediately updates auto-sync consent cache; disabling stops the interval, clears pending folder sync, detaches watch listeners, and unwatchAllManagedFolders without waiting for the previous 60s refresh window.</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G14" s="18" t="inlineStr">
         <is>
-          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync.</t>
+          <t>typecheck plus npm.cmd run dev:widget:backend checks GET/PATCH /api/me/privacy-consents and managed folder re-enable before local file sync. Verified with typecheck/product-rules/tauri-boundaries; targeted cargo local_files watch + SQLite diagnostics tests.</t>
         </is>
       </c>
       <c r="H14" s="18" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched.</t>
+          <t>Removes unsupported MANAGED_FOLDER_ACCESS/LOCAL_AGENT_MEMORY API enum usage; macOS logic untouched. Frontend consent runtime only; macOS native watch implementation untouched.</t>
         </is>
       </c>
       <c r="J14" s="18" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4574,6 +4574,28 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Managed folder consent revocation immediate stop</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npm.cmd run typecheck; npm.cmd run check:product-rules; npm.cmd run check:tauri-boundaries; cargo test --lib local_files::tests::watch_path_change_records_create_update_and_delete local_db::tests::sqlite_integrity_result_includes_storage_diagnostics</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>After localFolderEnabled is saved false, auto-sync interval stops, pending folder sync is cleared, watch listener is detached, and unwatchAllManagedFolders is requested immediately.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
